--- a/Results/PGNN_noVAE_noweights/PGNN_BMD_summary.xlsx
+++ b/Results/PGNN_noVAE_noweights/PGNN_BMD_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lsuma\Desktop\PGNN_results\PGNN_noVAE_noweights\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lsuma\Documents\GitHub\pLaplacian-Graph-NN\Results\PGNN_noVAE_noweights\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BB29F9-6DEF-43BB-AE0E-3AD0A4B3A6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C529D8F-F0E3-444B-921D-6E3372CBD43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2100" windowWidth="21600" windowHeight="11180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="16800" windowHeight="9670" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BMD_all_runs" sheetId="1" r:id="rId1"/>
@@ -1342,7 +1342,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
